--- a/public/sample_team_import_multisheet.xlsx
+++ b/public/sample_team_import_multisheet.xlsx
@@ -399,10 +399,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -412,6 +415,15 @@
       <c r="B1" t="str">
         <v>役割</v>
       </c>
+      <c r="C1" t="str">
+        <v>表示名</v>
+      </c>
+      <c r="D1" t="str">
+        <v>メール</v>
+      </c>
+      <c r="E1" t="str">
+        <v>初期パスワード</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -420,6 +432,15 @@
       <c r="B2" t="str">
         <v>リーダー</v>
       </c>
+      <c r="C2" t="str">
+        <v>山田 太郎</v>
+      </c>
+      <c r="D2" t="str">
+        <v>yamada@example.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Pass1234</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -428,6 +449,15 @@
       <c r="B3" t="str">
         <v>サブリーダー</v>
       </c>
+      <c r="C3" t="str">
+        <v>鈴木 花子</v>
+      </c>
+      <c r="D3" t="str">
+        <v>suzuki@example.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -436,20 +466,32 @@
       <c r="B4" t="str">
         <v/>
       </c>
+      <c r="C4" t="str">
+        <v>田中 一郎</v>
+      </c>
+      <c r="D4" t="str">
+        <v>tanaka@example.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,6 +501,15 @@
       <c r="B1" t="str">
         <v>役割</v>
       </c>
+      <c r="C1" t="str">
+        <v>表示名</v>
+      </c>
+      <c r="D1" t="str">
+        <v>メール</v>
+      </c>
+      <c r="E1" t="str">
+        <v>初期パスワード</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -467,6 +518,15 @@
       <c r="B2" t="str">
         <v>リーダー</v>
       </c>
+      <c r="C2" t="str">
+        <v>佐藤 二郎</v>
+      </c>
+      <c r="D2" t="str">
+        <v>sato@example.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -475,6 +535,15 @@
       <c r="B3" t="str">
         <v/>
       </c>
+      <c r="C3" t="str">
+        <v>伊藤 三郎</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ito@example.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -483,20 +552,32 @@
       <c r="B4" t="str">
         <v/>
       </c>
+      <c r="C4" t="str">
+        <v>加藤 六郎</v>
+      </c>
+      <c r="D4" t="str">
+        <v>kato@example.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:E3"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +587,15 @@
       <c r="B1" t="str">
         <v>役割</v>
       </c>
+      <c r="C1" t="str">
+        <v>表示名</v>
+      </c>
+      <c r="D1" t="str">
+        <v>メール</v>
+      </c>
+      <c r="E1" t="str">
+        <v>初期パスワード</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -514,6 +604,15 @@
       <c r="B2" t="str">
         <v>リーダー</v>
       </c>
+      <c r="C2" t="str">
+        <v>渡辺 四郎</v>
+      </c>
+      <c r="D2" t="str">
+        <v>watanabe@example.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -522,10 +621,19 @@
       <c r="B3" t="str">
         <v/>
       </c>
+      <c r="C3" t="str">
+        <v>小林 五郎</v>
+      </c>
+      <c r="D3" t="str">
+        <v>kobayashi@example.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>